--- a/files/serialized_asset_views/glassbeam.xlsx
+++ b/files/serialized_asset_views/glassbeam.xlsx
@@ -55,7 +55,7 @@
     <t>l3_modality_source_normalized</t>
   </si>
   <si>
-    <t>mel_id</t>
+    <t>mdm_model_id</t>
   </si>
   <si>
     <t>verified_model_name</t>
